--- a/search_query.xlsx
+++ b/search_query.xlsx
@@ -5,30 +5,45 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Desktop\Strelema\2025 codes\Media Monitoring Automation\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Desktop\Media-Monitoring\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D23637E-C1CA-4F96-BE93-0DADA2E1DB27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BF09433-9B94-48E6-9B00-B2BD13A4850D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5472" yWindow="3360" windowWidth="17280" windowHeight="8880" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="3" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Devendra Fadnavis" sheetId="1" r:id="rId1"/>
-    <sheet name="Siddharth Shirole" sheetId="5" r:id="rId2"/>
-    <sheet name="Ravindra Chavan" sheetId="3" r:id="rId3"/>
-    <sheet name="Ashish Shelar" sheetId="4" r:id="rId4"/>
+    <sheet name="Eknath Shinde" sheetId="7" r:id="rId2"/>
+    <sheet name="Prakash Abitkar" sheetId="6" r:id="rId3"/>
+    <sheet name="Ravindra Chavan" sheetId="3" r:id="rId4"/>
+    <sheet name="Ashish Shelar" sheetId="4" r:id="rId5"/>
+    <sheet name="Chandrakant Patil" sheetId="8" r:id="rId6"/>
+    <sheet name="Chandrashekhar Bawankule" sheetId="9" r:id="rId7"/>
+    <sheet name="Siddharth Shirole" sheetId="5" r:id="rId8"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="561" uniqueCount="516">
   <si>
     <t>devendra fadnavis</t>
   </si>
@@ -55,6 +70,1527 @@
   </si>
   <si>
     <t>सिद्धार्थ शिरोळे</t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस बातम्या</t>
+  </si>
+  <si>
+    <t>Devendra Fadnavis Chief Minister news</t>
+  </si>
+  <si>
+    <t>Devendra Fadnavis BJP news</t>
+  </si>
+  <si>
+    <t>Devendra Fadnavis politics news</t>
+  </si>
+  <si>
+    <t>Devendra Fadnavis Nagpur news</t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस समाचार</t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस ताजा समाचार</t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस नवीन बातम्या</t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस नागपूर बातम्या</t>
+  </si>
+  <si>
+    <t>ashish shelar latest news</t>
+  </si>
+  <si>
+    <t>ashish shelar marathi news</t>
+  </si>
+  <si>
+    <t>आशिष शेलार मंत्री</t>
+  </si>
+  <si>
+    <t>आशिष शेलार विषयी बातम्या</t>
+  </si>
+  <si>
+    <t>आशिष शेलार बातमी</t>
+  </si>
+  <si>
+    <t>आशिष शेलार बातमी मराठी</t>
+  </si>
+  <si>
+    <t>ashish shelar last week news</t>
+  </si>
+  <si>
+    <t>ashish shelar latest speech</t>
+  </si>
+  <si>
+    <t>ashish shelar mla</t>
+  </si>
+  <si>
+    <t>ashish shelar news</t>
+  </si>
+  <si>
+    <t>ashish shelar hindi news</t>
+  </si>
+  <si>
+    <t>Prakash Abitkar</t>
+  </si>
+  <si>
+    <t>प्रकाश आबिटकर</t>
+  </si>
+  <si>
+    <t>Prakash Abitkar news</t>
+  </si>
+  <si>
+    <t>प्रकाश आबिटकर बातम्या</t>
+  </si>
+  <si>
+    <t>प्रकाश आबिटकर मराठी बातम्या</t>
+  </si>
+  <si>
+    <t>Prakash Abitkar marathi news</t>
+  </si>
+  <si>
+    <t>प्रकाश आबिटकर इंग्रजी समाचार</t>
+  </si>
+  <si>
+    <t>Prakash Abitkar english news</t>
+  </si>
+  <si>
+    <t>प्रकाश आबिटकर हिंदी समाचार</t>
+  </si>
+  <si>
+    <t>Prakash Abitkar hindi news</t>
+  </si>
+  <si>
+    <t>Prakash Abitkar latest news</t>
+  </si>
+  <si>
+    <t>Prakash Abitkar activities</t>
+  </si>
+  <si>
+    <t>प्रकाश आबिटकर घटना</t>
+  </si>
+  <si>
+    <t>Prakash Abitkar speeches</t>
+  </si>
+  <si>
+    <t>प्रकाश आबिटकर भाषण</t>
+  </si>
+  <si>
+    <t>Prakash Abitkar statements</t>
+  </si>
+  <si>
+    <t>प्रकाश आबिटकर निवेदन</t>
+  </si>
+  <si>
+    <t>Prakash Abitkar controversies</t>
+  </si>
+  <si>
+    <t>प्रकाश आबिटकर वाद</t>
+  </si>
+  <si>
+    <t>Prakash Abitkar Radhanagari events</t>
+  </si>
+  <si>
+    <t>प्रकाश आबिटकर राधानगरी कार्यक्रम</t>
+  </si>
+  <si>
+    <t>Prakash Abitkar Maharashtra politics</t>
+  </si>
+  <si>
+    <t>प्रकाश आबिटकर महाराष्ट्र राजकारण</t>
+  </si>
+  <si>
+    <t>Prakash Abitkar social media</t>
+  </si>
+  <si>
+    <t>प्रकाश आबिटकर सोशल मीडिया</t>
+  </si>
+  <si>
+    <t>Prakash Abitkar public events</t>
+  </si>
+  <si>
+    <t>प्रकाश आबिटकर सार्वजनिक कार्यक्रम</t>
+  </si>
+  <si>
+    <t>Prakash Abitkar rural development</t>
+  </si>
+  <si>
+    <t>प्रकाश आबिटकर ग्रामीण विकास</t>
+  </si>
+  <si>
+    <t>Prakash Abitkar rallies</t>
+  </si>
+  <si>
+    <t>प्रकाश आबिटकर सभा</t>
+  </si>
+  <si>
+    <t>Prakash Abitkar Kolhapur events</t>
+  </si>
+  <si>
+    <t>प्रकाश आबिटकर कोल्हापूर कार्यक्रम</t>
+  </si>
+  <si>
+    <t>Prakash Abitkar Radhanagari meetings</t>
+  </si>
+  <si>
+    <t>प्रकाश आबिटकर राधानगरी बैठका</t>
+  </si>
+  <si>
+    <t>Prakash Abitkar health campaign</t>
+  </si>
+  <si>
+    <t>प्रकाश आबिटकर आरोग्य मोहीम</t>
+  </si>
+  <si>
+    <t>Prakash Abitkar temple events</t>
+  </si>
+  <si>
+    <t>प्रकाश आबिटकर मंदिर कार्यक्रम</t>
+  </si>
+  <si>
+    <t>Prakash Abitkar rural development events</t>
+  </si>
+  <si>
+    <t>प्रकाश आबिटकर ग्रामीण विकास कार्यक्रम</t>
+  </si>
+  <si>
+    <t>Prakash Abitkar water project events</t>
+  </si>
+  <si>
+    <t>प्रकाश आबिटकर जलप्रकल्प कार्यक्रम</t>
+  </si>
+  <si>
+    <t>Prakash Abitkar Shiv Sena events</t>
+  </si>
+  <si>
+    <t>प्रकाश आबिटकर शिवसेना कार्यक्रम</t>
+  </si>
+  <si>
+    <t>Eknath Shinde</t>
+  </si>
+  <si>
+    <t>Devendra Fadnavis news</t>
+  </si>
+  <si>
+    <t>Devendra Fadnavis latest news</t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस मुख्यमंत्री समाचार</t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस मुख्यमंत्री बातम्या</t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस भाजपा समाचार</t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस भाजप बातम्या</t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस राजनीति समाचार</t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस राजकीय बातम्या</t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस नागपुर समाचार</t>
+  </si>
+  <si>
+    <t>Devendra Fadnavis speech</t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस भाषण</t>
+  </si>
+  <si>
+    <t>Devendra Fadnavis reaction</t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस प्रतिक्रिया</t>
+  </si>
+  <si>
+    <t>Devendra Fadnavis opposition</t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस विपक्ष</t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस विरोधक</t>
+  </si>
+  <si>
+    <t>Devendra Fadnavis election</t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस चुनाव</t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस निवडणूक</t>
+  </si>
+  <si>
+    <t>Devendra Fadnavis campaign</t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस प्रचार</t>
+  </si>
+  <si>
+    <t>Devendra Fadnavis rally</t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस सभा</t>
+  </si>
+  <si>
+    <t>Devendra Fadnavis political decision</t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस राजनीतिक निर्णय</t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस राजकीय निर्णय</t>
+  </si>
+  <si>
+    <t>Devendra Fadnavis Shinde faction</t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस शिंदे गट</t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस शिंदे समूह</t>
+  </si>
+  <si>
+    <t>Devendra Fadnavis Uddhav Thackeray</t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस उद्धव ठाकरे</t>
+  </si>
+  <si>
+    <t>Devendra Fadnavis Legislative Council</t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस विधान परिषद</t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस विधानपरिषद</t>
+  </si>
+  <si>
+    <t>Devendra Fadnavis press conference</t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस पत्रकार परिषद</t>
+  </si>
+  <si>
+    <t>Devendra Fadnavis government</t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस सरकार</t>
+  </si>
+  <si>
+    <t>Devendra Fadnavis new project</t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस नया प्रकल्प</t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस नवा प्रकल्प</t>
+  </si>
+  <si>
+    <t>Devendra Fadnavis statement</t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस बयान</t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस विधान</t>
+  </si>
+  <si>
+    <t>Devendra Fadnavis politics</t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस राजनीति</t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस राजकारण</t>
+  </si>
+  <si>
+    <t>Devendra Fadnavis Maharashtra election</t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस महाराष्ट्र चुनाव</t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस महाराष्ट्र निवडणूक</t>
+  </si>
+  <si>
+    <t>Devendra Fadnavis opposition statement</t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस विपक्ष पर बयान</t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस विरोधकांवरील विधान</t>
+  </si>
+  <si>
+    <t>Devendra Fadnavis new scheme</t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस नई योजना</t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस नवीन योजना</t>
+  </si>
+  <si>
+    <t>Devendra Fadnavis government scheme</t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस सरकारी योजना</t>
+  </si>
+  <si>
+    <t>Devendra Fadnavis Shinde government</t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस शिंदे सरकार</t>
+  </si>
+  <si>
+    <t>Devendra Fadnavis public rally</t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस सार्वजनिक सभा</t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस जाहीर सभा</t>
+  </si>
+  <si>
+    <t>Devendra Fadnavis Maharashtra BJP</t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस महाराष्ट्र भाजपा</t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस महाराष्ट्र भाजप</t>
+  </si>
+  <si>
+    <t>Devendra Fadnavis vs Uddhav Thackeray</t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस बनाम उद्धव ठाकरे</t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस विरुद्ध उद्धव ठाकरे</t>
+  </si>
+  <si>
+    <t>Devendra Fadnavis alliance with Shinde</t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस का शिंदे के साथ गठबंधन</t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस शिंदे युती</t>
+  </si>
+  <si>
+    <t>Devendra Fadnavis speech highlights</t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस भाषण की मुख्य बातें</t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस भाषणातील ठळक मुद्दे</t>
+  </si>
+  <si>
+    <t>Devendra Fadnavis development project</t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस विकास प्रकल्प</t>
+  </si>
+  <si>
+    <t>Devendra Fadnavis infrastructure policy</t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस बुनियादी ढांचा नीति</t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस पायाभूत सुविधा धोरण</t>
+  </si>
+  <si>
+    <t>Devendra Fadnavis central government coordination</t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस केंद्र सरकार समन्वय</t>
+  </si>
+  <si>
+    <t>Devendra Fadnavis Modi government</t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस मोदी सरकार</t>
+  </si>
+  <si>
+    <t>Devendra Fadnavis on Rahul Gandhi</t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस राहुल गांधी पर</t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस राहुल गांधींवर</t>
+  </si>
+  <si>
+    <t>Devendra Fadnavis controversy</t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस विवाद</t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस वाद</t>
+  </si>
+  <si>
+    <t>Devendra Fadnavis MahaStride launch 2025</t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस महास्ट्राइड लॉन्च 2025</t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस महास्ट्राइड लाँच 2025</t>
+  </si>
+  <si>
+    <t>Devendra Fadnavis Pune Metro Phase-2 approval</t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस पुणे मेट्रो फेज-2 स्वीकृति</t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस पुणे मेट्रो फेज-2 मान्यता</t>
+  </si>
+  <si>
+    <t>Devendra Fadnavis Revenue Officers’ Handbook launch</t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस राजस्व अधिकारी हैंडबुक लॉन्च</t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस महसूल अधिकारी हँडबुक लाँच</t>
+  </si>
+  <si>
+    <t>Devendra Fadnavis Samvidhan Hatya Diwas 2025</t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस संविधान हत्या दिवस 2025</t>
+  </si>
+  <si>
+    <t>Devendra Fadnavis Nagpur firefighting vehicles</t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस नागपुर अग्निशमन वाहन</t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस नागपूर अग्निशमन वाहने</t>
+  </si>
+  <si>
+    <t>Devendra Fadnavis voter list controversy 2025</t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस मतदाता सूची विवाद 2025</t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस मतदार यादी वाद 2025</t>
+  </si>
+  <si>
+    <t>Devendra Fadnavis Uddhav Thackeray remarks</t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस उद्धव ठाकरे बयान</t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस उद्धव ठाकरे टीका</t>
+  </si>
+  <si>
+    <t>Devendra Fadnavis Maharashtra Radio Festival</t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस महाराष्ट्र रेडियो फेस्टिवल</t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस महाराष्ट्र रेडियो फेस्टिव्हल</t>
+  </si>
+  <si>
+    <t>Devendra Fadnavis NSEL settlement plan</t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस एनएसईएल निपटान योजना</t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस एनएसईएल सेटलमेंट योजना</t>
+  </si>
+  <si>
+    <t>Devendra Fadnavis Raj Thackeray meeting</t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस राज ठाकरे मुलाकात</t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस राज ठाकरे भेट</t>
+  </si>
+  <si>
+    <t>Devendra Fadnavis Chief Minister tenure 2014-2019</t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस मुख्यमंत्री कार्यकाल 2014-2019</t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस मुख्यमंत्री कार्यकाळ 2014-2019</t>
+  </si>
+  <si>
+    <t>Devendra Fadnavis role in 2022 Shiv Sena split</t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस 2022 शिवसेना विभाजन भूमिका</t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस 2022 शिवसेना फूट भूमिका</t>
+  </si>
+  <si>
+    <t>Devendra Fadnavis Nagpur South West constituency</t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस नागपुर साउथ वेस्ट निर्वाचन क्षेत्र</t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस नागपूर साउथ वेस्ट मतदारसंघ</t>
+  </si>
+  <si>
+    <t>Devendra Fadnavis BJP Maharashtra leadership</t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस भाजपा महाराष्ट्र नेतृत्व</t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस भाजप महाराष्ट्र नेतृत्व</t>
+  </si>
+  <si>
+    <t>Devendra Fadnavis infrastructure policies Maharashtra</t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस महाराष्ट्र बुनियादी ढांचा नीतियां</t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस महाराष्ट्र पायाभूत सुविधा धोरणे</t>
+  </si>
+  <si>
+    <t>Devendra Fadnavis 2014 election affidavit controversy</t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस 2014 चुनाव हलफनामा विवाद</t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस 2014 निवडणूक प्रत affidavit वाद</t>
+  </si>
+  <si>
+    <t>Devendra Fadnavis Mahayuti alliance strategy</t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस महायुति गठबंधन रणनीति</t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस महायुति आघाडी रणनीती</t>
+  </si>
+  <si>
+    <t>Devendra Fadnavis drought management Maharashtra</t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस महाराष्ट्र सूखा प्रबंधन</t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस महाराष्ट्र दुष्काळ व्यवस्थापन</t>
+  </si>
+  <si>
+    <t>Devendra Fadnavis RSS and ABVP background</t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस आरएसएस और एबीवीपी पृष्ठभूमि</t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस आरएसएस आणि एबीव्हीपी पार्श्वभूमी</t>
+  </si>
+  <si>
+    <t>Devendra Fadnavis Home Ministry portfolio 2024</t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस गृह मंत्रालय पोर्टफोलियो 2024</t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस गृह खाते पोर्टफोलियो 2024</t>
+  </si>
+  <si>
+    <t>Devendra Fadnavis Mumbai</t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस मुंबई</t>
+  </si>
+  <si>
+    <t>Devendra Fadnavis this week events 2025</t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस इस सप्ताह की घटनाएं 2025</t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस या आठवड्याचे कार्यक्रम 2025</t>
+  </si>
+  <si>
+    <t>Devendra Fadnavis Pandharpur Wari 2025</t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस पंढरपूर वारी 2025</t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस पंढरी वारी 2025</t>
+  </si>
+  <si>
+    <t>Devendra Fadnavis environmental initiative 2025</t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस पर्यावरण पहल 2025</t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस पर्यावरण उपक्रम 2025</t>
+  </si>
+  <si>
+    <t>Devendra Fadnavis Aarogya Wari 2025</t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस आरोग्य वारी 2025</t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस स्वास्थ्य वारी 2025</t>
+  </si>
+  <si>
+    <t>Devendra Fadnavis voter list spike controversy 2025</t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस मतदाता सूची वृद्धि विवाद 2025</t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस मतदार यादी वाढ वाद 2025</t>
+  </si>
+  <si>
+    <t>Devendra Fadnavis Marathi language controversy 2025</t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस मराठी भाषा विवाद 2025</t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस मराठी भाषा वाद 2025</t>
+  </si>
+  <si>
+    <t>Devendra Fadnavis political activities July 2025</t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस जुलाई 2025 राजनीतिक गतिविधियां</t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस जुलै 2025 राजकीय हालचाली</t>
+  </si>
+  <si>
+    <t>Devendra Fadnavis public engagements 2025</t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस सार्वजनिक सहभाग 2025</t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस जनसंपर्क 2025</t>
+  </si>
+  <si>
+    <t>Devendra Fadnavis Maharashtra governance 2025</t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस महाराष्ट्र शासन 2025</t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस महाराष्ट्र प्रशासन 2025</t>
+  </si>
+  <si>
+    <t>Devendra Fadnavis policy decisions 2025</t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस नीति निर्णय 2025</t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस धोरण निर्णय 2025</t>
+  </si>
+  <si>
+    <t>Devendra Fadnavis rural development initiatives</t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस ग्रामीण विकास पहल</t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस ग्रामीण विकास उपक्रम</t>
+  </si>
+  <si>
+    <t>Devendra Fadnavis urban infrastructure projects</t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस शहरी बुनियादी ढांचा परियोजनाएं</t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस शहरी पायाभूत प्रकल्प</t>
+  </si>
+  <si>
+    <t>Devendra Fadnavis economic policies Maharashtra</t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस महाराष्ट्र आर्थिक नीतियां</t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस महाराष्ट्र आर्थिक धोरणे</t>
+  </si>
+  <si>
+    <t>Devendra Fadnavis social welfare schemes 2025</t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस सामाजिक कल्याण योजनाएं 2025</t>
+  </si>
+  <si>
+    <t>देवेंद्र फडणवीस सामाजिक कल्याण योजना 2025</t>
+  </si>
+  <si>
+    <t>siddharth shirole news</t>
+  </si>
+  <si>
+    <t>सिद्धार्थ शिरोळे बातम्या</t>
+  </si>
+  <si>
+    <t>siddharth shirole latest news</t>
+  </si>
+  <si>
+    <t>सिद्धार्थ शिरोळे नवीनतम बातम्या</t>
+  </si>
+  <si>
+    <t>siddharth shirole Marathi news</t>
+  </si>
+  <si>
+    <t>सिद्धार्थ शिरोळे मराठी बातम्या</t>
+  </si>
+  <si>
+    <t xml:space="preserve">siddharth shirole Hindi news </t>
+  </si>
+  <si>
+    <t xml:space="preserve">सिद्धार्थ शिरोळे हिंदी समाचार </t>
+  </si>
+  <si>
+    <t xml:space="preserve">siddharth shirole English news </t>
+  </si>
+  <si>
+    <t xml:space="preserve">siddharth shirole BJP </t>
+  </si>
+  <si>
+    <t xml:space="preserve">सिद्धार्थ शिरोळे इंग्रजी समाचार </t>
+  </si>
+  <si>
+    <t>siddharth shirole interview</t>
+  </si>
+  <si>
+    <t>सिद्धार्थ शिरोळे मुलाखत</t>
+  </si>
+  <si>
+    <t>siddharth shirole speech</t>
+  </si>
+  <si>
+    <t>सिद्धार्थ शिरोळे भाषण</t>
+  </si>
+  <si>
+    <t>siddharth shirole press conference</t>
+  </si>
+  <si>
+    <t>सिद्धार्थ शिरोळे पत्रकार परिषद</t>
+  </si>
+  <si>
+    <t>siddharth shirole news today</t>
+  </si>
+  <si>
+    <t>सिद्धार्थ शिरोळे आजच्या बातम्या</t>
+  </si>
+  <si>
+    <t>siddharth shirole work in pune</t>
+  </si>
+  <si>
+    <t>सिद्धार्थ शिरोळे यांचे पुण्यातील कार्य</t>
+  </si>
+  <si>
+    <t>siddharth shirole achievements</t>
+  </si>
+  <si>
+    <t>सिद्धार्थ शिरोळे यांची कामगिरी</t>
+  </si>
+  <si>
+    <t>siddharth shirole development work</t>
+  </si>
+  <si>
+    <t>सिद्धार्थ शिरोळे विकास कामे</t>
+  </si>
+  <si>
+    <t>siddharth shirole reviews</t>
+  </si>
+  <si>
+    <t>सिद्धार्थ शिरोळे जनमत</t>
+  </si>
+  <si>
+    <t>siddharth shirole good or bad</t>
+  </si>
+  <si>
+    <t>सिद्धार्थ शिरोळे चांगले की वाईट</t>
+  </si>
+  <si>
+    <t>siddharth shirole criticism</t>
+  </si>
+  <si>
+    <t>सिद्धार्थ शिरोळे टीका</t>
+  </si>
+  <si>
+    <t>siddharth shirole public opinion</t>
+  </si>
+  <si>
+    <t>सिद्धार्थ शिरोळे यांच्याबद्दल लोकांचे मत</t>
+  </si>
+  <si>
+    <t>सिद्धार्थ शिरोले कौन है</t>
+  </si>
+  <si>
+    <t>सिद्धार्थ शिरोले का कार्य</t>
+  </si>
+  <si>
+    <t>सिद्धार्थ शिरोले बीजेपी नेता</t>
+  </si>
+  <si>
+    <t>सिद्धार्थ शिरोले पुणे से विधायक</t>
+  </si>
+  <si>
+    <t>सिद्धार्थ शिरोले पर खबरें</t>
+  </si>
+  <si>
+    <t>siddharth shirole shivajinagar</t>
+  </si>
+  <si>
+    <t>सिद्धार्थ शिरोळे शिवाजीनगर</t>
+  </si>
+  <si>
+    <t>siddharth shirole shivajinagar mla</t>
+  </si>
+  <si>
+    <t>shivajinagar mla siddharth shirole work</t>
+  </si>
+  <si>
+    <t>शिवाजीनगर आमदार सिद्धार्थ शिरोळे</t>
+  </si>
+  <si>
+    <t>सिद्धार्थ शिरोळे मतदारसंघ</t>
+  </si>
+  <si>
+    <t>siddharth shirole pune issues</t>
+  </si>
+  <si>
+    <t>सिद्धार्थ शिरोळे पुणे समस्या</t>
+  </si>
+  <si>
+    <t>siddharth shirole civic problems</t>
+  </si>
+  <si>
+    <t>सिद्धार्थ शिरोळे नागरी समस्या</t>
+  </si>
+  <si>
+    <t>siddharth shirole political career</t>
+  </si>
+  <si>
+    <t>सिद्धार्थ शिरोळे यांचा राजकीय प्रवास</t>
+  </si>
+  <si>
+    <t>siddharth shirole youth leader</t>
+  </si>
+  <si>
+    <t>bjp young leader siddharth shirole</t>
+  </si>
+  <si>
+    <t>siddharth shirole party role</t>
+  </si>
+  <si>
+    <t>सिद्धार्थ शिरोळे पक्षातील भूमिका</t>
+  </si>
+  <si>
+    <t>siddharth shirole public programs</t>
+  </si>
+  <si>
+    <t>सिद्धार्थ शिरोळे जनसंपर्क दौरा</t>
+  </si>
+  <si>
+    <t>siddharth shirole next election</t>
+  </si>
+  <si>
+    <t>सिद्धार्थ शिरोळे पुढील निवडणूक</t>
+  </si>
+  <si>
+    <t>siddharth shirole 2024 lok sabha</t>
+  </si>
+  <si>
+    <t>siddharth shirole assembly elections 2024</t>
+  </si>
+  <si>
+    <t>सिद्धार्थ शिरोळे निवडणूक 2024</t>
+  </si>
+  <si>
+    <t>siddharth shirole vs congress candidate</t>
+  </si>
+  <si>
+    <t>siddharth shirole controversy</t>
+  </si>
+  <si>
+    <t>सिद्धार्थ शिरोळे वाद</t>
+  </si>
+  <si>
+    <t>siddharth shirole criticism news</t>
+  </si>
+  <si>
+    <t>सिद्धार्थ शिरोळे टीका बातम्या</t>
+  </si>
+  <si>
+    <t>siddharth shirole scam</t>
+  </si>
+  <si>
+    <t>सिद्धार्थ शिरोळे घोटाळा</t>
+  </si>
+  <si>
+    <t>siddharth shirole smart city work</t>
+  </si>
+  <si>
+    <t>सिद्धार्थ शिरोळे स्मार्ट सिटी काम</t>
+  </si>
+  <si>
+    <t>siddharth shirole metro project</t>
+  </si>
+  <si>
+    <t>पुणे मेट्रो सिद्धार्थ शिरोळे</t>
+  </si>
+  <si>
+    <t>siddharth shirole infrastructure projects</t>
+  </si>
+  <si>
+    <t>सिद्धार्थ शिरोळे पायाभूत सुविधा</t>
+  </si>
+  <si>
+    <t>siddharth shirole budget utilization</t>
+  </si>
+  <si>
+    <t>सिद्धार्थ शिरोळे निधी वापर</t>
+  </si>
+  <si>
+    <t>एकनाथ शिंदे</t>
+  </si>
+  <si>
+    <t>Eknath Shinde news</t>
+  </si>
+  <si>
+    <t>एकनाथ शिंदे समाचार</t>
+  </si>
+  <si>
+    <t>एकनाथ शिंदे बातम्या</t>
+  </si>
+  <si>
+    <t>Eknath Shinde latest news</t>
+  </si>
+  <si>
+    <t>एकनाथ शिंदे ताजा समाचार</t>
+  </si>
+  <si>
+    <t>एकनाथ शिंदे नवीन बातम्या</t>
+  </si>
+  <si>
+    <t>Eknath Shinde Deputy Chief Minister</t>
+  </si>
+  <si>
+    <t>एकनाथ शिंदे उपमुख्यमंत्री</t>
+  </si>
+  <si>
+    <t>Eknath Shinde Shiv Sena</t>
+  </si>
+  <si>
+    <t>एकनाथ शिंदे शिवसेना</t>
+  </si>
+  <si>
+    <t>Eknath Shinde politics</t>
+  </si>
+  <si>
+    <t>एकनाथ शिंदे राजनीति</t>
+  </si>
+  <si>
+    <t>एकनाथ शिंदे राजकीय</t>
+  </si>
+  <si>
+    <t>Eknath Shinde Thane</t>
+  </si>
+  <si>
+    <t>एकनाथ शिंदे ठाणे</t>
+  </si>
+  <si>
+    <t>Eknath Shinde speech</t>
+  </si>
+  <si>
+    <t>एकनाथ शिंदे भाषण</t>
+  </si>
+  <si>
+    <t>Eknath Shinde reaction</t>
+  </si>
+  <si>
+    <t>एकनाथ शिंदे प्रतिक्रिया</t>
+  </si>
+  <si>
+    <t>Eknath Shinde opposition</t>
+  </si>
+  <si>
+    <t>एकनाथ शिंदे विपक्ष</t>
+  </si>
+  <si>
+    <t>एकनाथ शिंदे विरोधक</t>
+  </si>
+  <si>
+    <t>Eknath Shinde election</t>
+  </si>
+  <si>
+    <t>एकनाथ शिंदे चुनाव</t>
+  </si>
+  <si>
+    <t>एकनाथ शिंदे निवडणूक</t>
+  </si>
+  <si>
+    <t>Eknath Shinde campaign</t>
+  </si>
+  <si>
+    <t>एकनाथ शिंदे प्रचार</t>
+  </si>
+  <si>
+    <t>Eknath Shinde rally</t>
+  </si>
+  <si>
+    <t>एकनाथ शिंदे सभा</t>
+  </si>
+  <si>
+    <t>Eknath Shinde political decision</t>
+  </si>
+  <si>
+    <t>एकनाथ शिंदे राजनीतिक निर्णय</t>
+  </si>
+  <si>
+    <t>एकनाथ शिंदे राजकीय निर्णय</t>
+  </si>
+  <si>
+    <t>Eknath Shinde Uddhav Thackeray</t>
+  </si>
+  <si>
+    <t>एकनाथ शिंदे उद्धव ठाकरे</t>
+  </si>
+  <si>
+    <t>Eknath Shinde Legislative Council</t>
+  </si>
+  <si>
+    <t>एकनाथ शिंदे विधान परिषद</t>
+  </si>
+  <si>
+    <t>एकनाथ शिंदे विधानपरिषद</t>
+  </si>
+  <si>
+    <t>Eknath Shinde press conference</t>
+  </si>
+  <si>
+    <t>एकनाथ शिंदे पत्रकार परिषद</t>
+  </si>
+  <si>
+    <t>Eknath Shinde government</t>
+  </si>
+  <si>
+    <t>एकनाथ शिंदे सरकार</t>
+  </si>
+  <si>
+    <t>Eknath Shinde new project</t>
+  </si>
+  <si>
+    <t>एकनाथ शिंदे नया प्रकल्प</t>
+  </si>
+  <si>
+    <t>एकनाथ शिंदे नवा प्रकल्प</t>
+  </si>
+  <si>
+    <t>Eknath Shinde statement</t>
+  </si>
+  <si>
+    <t>एकनाथ शिंदे बयान</t>
+  </si>
+  <si>
+    <t>एकनाथ शिंदे विधान</t>
+  </si>
+  <si>
+    <t>एकनाथ शिंदे राजकारण</t>
+  </si>
+  <si>
+    <t>Eknath Shinde Maharashtra election</t>
+  </si>
+  <si>
+    <t>एकनाथ शिंदे महाराष्ट्र चुनाव</t>
+  </si>
+  <si>
+    <t>एकनाथ शिंदे महाराष्ट्र निवडणूक</t>
+  </si>
+  <si>
+    <t>Eknath Shinde opposition statement</t>
+  </si>
+  <si>
+    <t>एकनाथ शिंदे विपक्ष पर बयान</t>
+  </si>
+  <si>
+    <t>एकनाथ शिंदे विरोधकांवरील विधान</t>
+  </si>
+  <si>
+    <t>Eknath Shinde new scheme</t>
+  </si>
+  <si>
+    <t>एकनाथ शिंदे नई योजना</t>
+  </si>
+  <si>
+    <t>एकनाथ शिंदे नवीन योजना</t>
+  </si>
+  <si>
+    <t>Eknath Shinde government scheme</t>
+  </si>
+  <si>
+    <t>एकनाथ शिंदे सरकारी योजना</t>
+  </si>
+  <si>
+    <t>Eknath Shinde Mahayuti alliance</t>
+  </si>
+  <si>
+    <t>एकनाथ शिंदे महायुति गठबंधन</t>
+  </si>
+  <si>
+    <t>एकनाथ शिंदे महायुति आघाडी</t>
+  </si>
+  <si>
+    <t>Eknath Shinde public rally</t>
+  </si>
+  <si>
+    <t>एकनाथ शिंदे सार्वजनिक सभा</t>
+  </si>
+  <si>
+    <t>एकनाथ शिंदे जाहीर सभा</t>
+  </si>
+  <si>
+    <t>Eknath Shinde Maharashtra Shiv Sena</t>
+  </si>
+  <si>
+    <t>एकनाथ शिंदे महाराष्ट्र शिवसेना</t>
+  </si>
+  <si>
+    <t>Eknath Shinde vs Uddhav Thackeray</t>
+  </si>
+  <si>
+    <t>एकनाथ शिंदे बनाम उद्धव ठाकरे</t>
+  </si>
+  <si>
+    <t>एकनाथ शिंदे विरुद्ध उद्धव ठाकरे</t>
+  </si>
+  <si>
+    <t>Eknath Shinde alliance with Fadnavis</t>
+  </si>
+  <si>
+    <t>एकनाथ शिंदे का फडणवीस के साथ गठबंधन</t>
+  </si>
+  <si>
+    <t>एकनाथ शिंदे फडणवीस युती</t>
+  </si>
+  <si>
+    <t>Eknath Shinde speech highlights</t>
+  </si>
+  <si>
+    <t>एकनाथ शिंदे भाषण की मुख्य बातें</t>
+  </si>
+  <si>
+    <t>एकनाथ शिंदे भाषणातील ठळक मुद्दे</t>
+  </si>
+  <si>
+    <t>Eknath Shinde development project</t>
+  </si>
+  <si>
+    <t>एकनाथ शिंदे विकास प्रकल्प</t>
+  </si>
+  <si>
+    <t>Eknath Shinde infrastructure policy</t>
+  </si>
+  <si>
+    <t>एकनाथ शिंदे बुनियादी ढांचा नीति</t>
+  </si>
+  <si>
+    <t>एकनाथ शिंदे पायाभूत सुविधा धोरण</t>
+  </si>
+  <si>
+    <t>Eknath Shinde central government coordination</t>
+  </si>
+  <si>
+    <t>एकनाथ शिंदे केंद्र सरकार समन्वय</t>
+  </si>
+  <si>
+    <t>Eknath Shinde Modi government</t>
+  </si>
+  <si>
+    <t>एकनाथ शिंदे मोदी सरकार</t>
+  </si>
+  <si>
+    <t>Eknath Shinde on Rahul Gandhi</t>
+  </si>
+  <si>
+    <t>एकनाथ शिंदे राहुल गांधी पर</t>
+  </si>
+  <si>
+    <t>एकनाथ शिंदे राहुल गांधींवर</t>
+  </si>
+  <si>
+    <t>Eknath Shinde controversy</t>
+  </si>
+  <si>
+    <t>एकनाथ शिंदे विवाद</t>
+  </si>
+  <si>
+    <t>एकनाथ शिंदे वाद</t>
+  </si>
+  <si>
+    <t>Eknath Shinde Chief Minister tenure 2022-2024</t>
+  </si>
+  <si>
+    <t>एकनाथ शिंदे मुख्यमंत्री कार्यकाल 2022-2024</t>
+  </si>
+  <si>
+    <t>एकनाथ शिंदे मुख्यमंत्री कार्यकाळ 2022-2024</t>
+  </si>
+  <si>
+    <t>Eknath Shinde role in 2022 Shiv Sena split</t>
+  </si>
+  <si>
+    <t>एकनाथ शिंदे 2022 शिवसेना विभाजन भूमिका</t>
+  </si>
+  <si>
+    <t>एकनाथ शिंदे 2022 शिवसेना फूट भूमिका</t>
+  </si>
+  <si>
+    <t>Eknath Shinde Thane constituency</t>
+  </si>
+  <si>
+    <t>एकनाथ शिंदे ठाणे निर्वाचन क्षेत्र</t>
+  </si>
+  <si>
+    <t>एकनाथ शिंदे ठाणे मतदारसंघ</t>
+  </si>
+  <si>
+    <t>Eknath Shinde Shiv Sena leadership</t>
+  </si>
+  <si>
+    <t>एकनाथ शिंदे शिवसेना नेतृत्व</t>
+  </si>
+  <si>
+    <t>Eknath Shinde infrastructure policies Maharashtra</t>
+  </si>
+  <si>
+    <t>एकनाथ शिंदे महाराष्ट्र बुनियादी ढांचा नीतियां</t>
+  </si>
+  <si>
+    <t>एकनाथ शिंदे महाराष्ट्र पायाभूत सुविधा धोरणे</t>
+  </si>
+  <si>
+    <t>Eknath Shinde Mahayuti alliance strategy</t>
+  </si>
+  <si>
+    <t>एकनाथ शिंदे महायुति गठबंधन रणनीति</t>
+  </si>
+  <si>
+    <t>एकनाथ शिंदे महायुति आघाडी रणनीती</t>
+  </si>
+  <si>
+    <t>Eknath Shinde drought management Maharashtra</t>
+  </si>
+  <si>
+    <t>एकनाथ शिंदे महाराष्ट्र सूखा प्रबंधन</t>
+  </si>
+  <si>
+    <t>एकनाथ शिंदे महाराष्ट्र दुष्काळ व्यवस्थापन</t>
+  </si>
+  <si>
+    <t>Eknath Shinde this week events 2025</t>
+  </si>
+  <si>
+    <t>एकनाथ शिंदे इस सप्ताह की घटनाएं 2025</t>
+  </si>
+  <si>
+    <t>एकनाथ शिंदे या आठवड्याचे कार्यक्रम 2025</t>
+  </si>
+  <si>
+    <t>Eknath Shinde Jai Gujarat controversy 2025</t>
+  </si>
+  <si>
+    <t>एकनाथ शिंदे जय गुजरात विवाद 2025</t>
+  </si>
+  <si>
+    <t>एकनाथ शिंदे जय गुजरात वाद 2025</t>
+  </si>
+  <si>
+    <t>Eknath Shinde Ashadi Ekadashi 2025</t>
+  </si>
+  <si>
+    <t>एकनाथ शिंदे आषाढी एकादशी 2025</t>
+  </si>
+  <si>
+    <t>Eknath Shinde Three Rivers Revitalization Project 2025</t>
+  </si>
+  <si>
+    <t>एकनाथ शिंदे तीन नदियों का पुनरुज्जन प्रकल्प 2025</t>
+  </si>
+  <si>
+    <t>एकनाथ शिंदे तीन नद्यांचा पुनरुज्जन प्रकल्प 2025</t>
+  </si>
+  <si>
+    <t>Eknath Shinde Raj Thackeray remarks 2025</t>
+  </si>
+  <si>
+    <t>एकनाथ शिंदे राज ठाकरे बयान 2025</t>
+  </si>
+  <si>
+    <t>एकनाथ शिंदे राज ठाकरे टीका 2025</t>
+  </si>
+  <si>
+    <t>Eknath Shinde Uddhav Thackeray victory rally response 2025</t>
+  </si>
+  <si>
+    <t>एकनाथ शिंदे उद्धव ठाकरे विजय रैली प्रतिक्रिया 2025</t>
+  </si>
+  <si>
+    <t>एकनाथ शिंदे उद्धव ठाकरे विजयी सभा प्रतिक्रिया 2025</t>
+  </si>
+  <si>
+    <t>Eknath Shinde Marathi language defense 2025</t>
+  </si>
+  <si>
+    <t>एकनाथ शिंदे मराठी भाषा संरक्षण 2025</t>
+  </si>
+  <si>
+    <t>Eknath Shinde political activities July 2025</t>
+  </si>
+  <si>
+    <t>एकनाथ शिंदे जुलाई 2025 राजनीतिक गतिविधियां</t>
+  </si>
+  <si>
+    <t>एकनाथ शिंदे जुलै 2025 राजकीय हालचाली</t>
+  </si>
+  <si>
+    <t>Eknath Shinde public engagements 2025</t>
+  </si>
+  <si>
+    <t>एकनाथ शिंदे सार्वजनिक सहभाग 2025</t>
+  </si>
+  <si>
+    <t>एकनाथ शिंदे जनसंपर्क 2025</t>
+  </si>
+  <si>
+    <t>Eknath Shinde Maharashtra governance 2025</t>
+  </si>
+  <si>
+    <t>एकनाथ शिंदे महाराष्ट्र शासन 2025</t>
+  </si>
+  <si>
+    <t>एकनाथ शिंदे महाराष्ट्र प्रशासन 2025</t>
+  </si>
+  <si>
+    <t>Eknath Shinde policy decisions 2025</t>
+  </si>
+  <si>
+    <t>एकनाथ शिंदे नीति निर्णय 2025</t>
+  </si>
+  <si>
+    <t>एकनाथ शिंदे धोरण निर्णय 2025</t>
+  </si>
+  <si>
+    <t>Eknath Shinde rural development initiatives</t>
+  </si>
+  <si>
+    <t>एकनाथ शिंदे ग्रामीण विकास पहल</t>
+  </si>
+  <si>
+    <t>एकनाथ शिंदे ग्रामीण विकास उपक्रम</t>
+  </si>
+  <si>
+    <t>Eknath Shinde urban infrastructure projects</t>
+  </si>
+  <si>
+    <t>एकनाथ शिंदे शहरी बुनियादी ढांचा परियोजनाएं</t>
+  </si>
+  <si>
+    <t>एकनाथ शिंदे शहरी पायाभूत प्रकल्प</t>
+  </si>
+  <si>
+    <t>Eknath Shinde economic policies Maharashtra</t>
+  </si>
+  <si>
+    <t>एकनाथ शिंदे महाराष्ट्र आर्थिक नीतियां</t>
+  </si>
+  <si>
+    <t>एकनाथ शिंदे महाराष्ट्र आर्थिक धोरणे</t>
+  </si>
+  <si>
+    <t>Eknath Shinde social welfare schemes 2025</t>
+  </si>
+  <si>
+    <t>एकनाथ शिंदे सामाजिक कल्याण योजनाएं 2025</t>
+  </si>
+  <si>
+    <t>एकनाथ शिंदे सामाजिक कल्याण योजना 2025</t>
+  </si>
+  <si>
+    <t>Eknath Shinde Mukhyamantri Majhi Ladki Bahin Yojana</t>
+  </si>
+  <si>
+    <t>एकनाथ शिंदे मुख्यमंत्री माझी लाडकी बहीण योजना</t>
+  </si>
+  <si>
+    <t>Eknath Shinde Shiv Kosh Trust 2025</t>
+  </si>
+  <si>
+    <t>एकनाथ शिंदे शिवकोश ट्रस्ट 2025</t>
+  </si>
+  <si>
+    <t>Eknath Shinde Anand Dighe statue Thane</t>
+  </si>
+  <si>
+    <t>एकनाथ शिंदे आनंद दिघे पुतळा ठाणे</t>
+  </si>
+  <si>
+    <t>रविंद्र चव्हाण भाजपा प्रदेशाध्यक्ष</t>
+  </si>
+  <si>
+    <t>ravindra chavan BJP President</t>
+  </si>
+  <si>
+    <t>ravindra chavan news</t>
+  </si>
+  <si>
+    <t>रविंद्र चव्हाण बातम्या</t>
+  </si>
+  <si>
+    <t>रविंद्र चव्हाण मराठी बातम्या</t>
+  </si>
+  <si>
+    <t>ravindra chavan marathi news</t>
+  </si>
+  <si>
+    <t>रविंद्र चव्हाण इंग्रजी समाचार</t>
+  </si>
+  <si>
+    <t>ravindra chavan english news</t>
+  </si>
+  <si>
+    <t>रविंद्र चव्हाण हिंदी समाचार</t>
+  </si>
+  <si>
+    <t>ravindra chavan hindi news</t>
+  </si>
+  <si>
+    <t>ravindra chavan latest news</t>
   </si>
 </sst>
 </file>
@@ -381,7 +1917,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A219"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.88671875" bestFit="1" customWidth="1"/>
@@ -402,14 +1938,1094 @@
         <v>2</v>
       </c>
     </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A53" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A54" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A55" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A56" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A57" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A58" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A59" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A60" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A61" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A62" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A63" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A64" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A65" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A66" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A67" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A68" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A69" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A70" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A71" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A72" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="77" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="78" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="80" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A80" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A81" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A82" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A83" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A84" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A85" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="86" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A86" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="87" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A87" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="88" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A88" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="89" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A89" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="90" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A90" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="91" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A91" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="92" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A92" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="93" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A93" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="94" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A94" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="95" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A95" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="96" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A96" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="97" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A97" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="98" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A98" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="99" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A99" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="100" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A100" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="101" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A101" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="102" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A102" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="103" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A103" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="104" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A104" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="105" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A105" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="106" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A106" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="107" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A107" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="108" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A108" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="109" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A109" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="110" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A110" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="111" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A111" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="112" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A112" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="113" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A113" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="114" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A114" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="115" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A115" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="116" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A116" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="117" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A117" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="118" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A118" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="119" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A119" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="120" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A120" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="121" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A121" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="122" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A122" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="123" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A123" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="124" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A124" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="125" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A125" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="126" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A126" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="127" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A127" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="128" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A128" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="129" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A129" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="130" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A130" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="131" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A131" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="132" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A132" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="133" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A133" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="134" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A134" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="135" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A135" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="136" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A136" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="137" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A137" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="138" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A138" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="139" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A139" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="140" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A140" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="141" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A141" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="142" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A142" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="143" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A143" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="144" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A144" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="145" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A145" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="146" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A146" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="147" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A147" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="148" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A148" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="149" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A149" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="150" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A150" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="151" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A151" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="152" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A152" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="153" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A153" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="154" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A154" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="155" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A155" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="156" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A156" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="157" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A157" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="158" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A158" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="159" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A159" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="160" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A160" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="161" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A161" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="162" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A162" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="163" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A163" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="164" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A164" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="165" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A165" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="166" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A166" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="167" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A167" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="168" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A168" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="169" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A169" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="170" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A170" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="171" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A171" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="172" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A172" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="173" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A173" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="174" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A174" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="175" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A175" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="176" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A176" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="177" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A177" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="178" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A178" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="179" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A179" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="180" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A180" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="181" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A181" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="182" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A182" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="183" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A183" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="184" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A184" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="185" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A185" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="186" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A186" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="187" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A187" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="188" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A188" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="189" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A189" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="190" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A190" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="191" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A191" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="192" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A192" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="193" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A193" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="194" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A194" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="195" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A195" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="196" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A196" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="197" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A197" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="198" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A198" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="199" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A199" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="200" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A200" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="201" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A201" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="202" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A202" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="203" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A203" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="204" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A204" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="205" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A205" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="206" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A206" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="207" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A207" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="208" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A208" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="209" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A209" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="210" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A210" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="211" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A211" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="212" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A212" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="213" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A213" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="214" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A214" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="215" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A215" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="216" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A216" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="217" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A217" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="218" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A218" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="219" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A219" t="s">
+        <v>267</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86D4577D-FE10-42FD-B10A-D28414797A5F}">
-  <dimension ref="A1:A3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E8F7DD1D-0DFC-440F-988C-050CA65FFA2F}">
+  <dimension ref="A1:A185"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
@@ -419,12 +3035,922 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>74</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>344</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A53" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A54" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A55" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A56" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A57" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A58" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A59" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A60" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A61" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A62" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A63" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A64" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A65" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A66" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A67" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A68" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A69" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A70" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A71" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A72" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="77" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="78" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="80" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A80" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A81" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A82" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A83" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A84" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A85" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="86" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A86" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="87" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A87" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="88" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A88" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="89" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A89" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="90" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A90" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="91" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A91" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="92" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A92" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="93" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A93" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="94" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A94" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="95" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A95" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="96" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A96" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="97" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A97" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="98" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A98" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="99" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A99" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="100" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A100" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="101" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A101" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="102" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A102" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="103" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A103" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="104" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A104" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="105" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A105" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="106" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A106" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="107" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A107" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="108" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A108" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="109" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A109" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="110" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A110" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="111" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A111" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="112" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A112" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="113" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A113" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="114" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A114" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="115" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A115" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="116" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A116" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="117" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A117" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="118" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A118" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="119" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A119" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="120" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A120" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="121" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A121" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="122" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A122" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="123" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A123" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="124" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A124" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="125" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A125" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="126" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A126" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="127" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A127" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="128" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A128" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="129" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A129" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="130" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A130" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="131" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A131" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="132" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A132" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="133" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A133" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="134" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A134" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="135" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A135" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="136" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A136" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="137" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A137" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="138" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A138" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="139" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A139" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="140" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A140" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="141" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A141" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="142" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A142" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="143" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A143" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="144" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A144" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="145" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A145" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="146" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A146" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="147" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A147" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="148" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A148" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="149" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A149" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="150" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A150" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="151" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A151" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="152" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A152" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="153" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A153" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="154" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A154" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="155" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A155" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="156" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A156" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="157" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A157" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="158" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A158" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="159" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A159" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="160" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A160" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="161" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A161" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="162" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A162" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="163" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A163" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="164" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A164" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="165" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A165" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="166" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A166" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="167" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A167" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="168" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A168" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="169" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A169" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="170" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A170" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="171" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A171" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="172" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A172" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="173" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A173" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="174" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A174" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="175" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A175" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="176" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A176" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="177" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A177" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="178" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A178" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="179" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A179" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="180" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A180" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="181" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A181" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="182" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A182" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="183" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A183" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="184" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A184" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="185" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A185" t="s">
+        <v>504</v>
       </c>
     </row>
   </sheetData>
@@ -433,8 +3959,258 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C494B66-AEA5-4CCE-888E-96E7151CA2B5}">
+  <dimension ref="A1:A48"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
+        <v>73</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{13BB4D98-1E3A-4E3C-ACBA-9B32A23C1612}">
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A14"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14" bestFit="1" customWidth="1"/>
@@ -455,14 +4231,69 @@
         <v>4</v>
       </c>
     </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>515</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{20836306-9997-450D-A55C-BA5D93912EB9}">
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A14"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.5546875" bestFit="1" customWidth="1"/>
@@ -483,6 +4314,496 @@
         <v>6</v>
       </c>
     </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>28</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3999BA3D-14F7-4974-A4C1-C319E42C52A3}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C323B3F7-4FF2-40F4-B949-CB50AFBFD4BF}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86D4577D-FE10-42FD-B10A-D28414797A5F}">
+  <dimension ref="A1:A79"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A53" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A54" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A55" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A56" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A57" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A58" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A59" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A60" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A61" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A62" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A63" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A64" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A65" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A66" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A67" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A68" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A69" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A70" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A71" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A72" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="77" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="78" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
+        <v>343</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
